--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -488,7 +488,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-height|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-height|2.2.0</t>
   </si>
   <si>
     <t>Observation.meta.security</t>
@@ -656,7 +656,7 @@
     <t>bodyposition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-height-body-position|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-height-body-position|2.2.0}
 </t>
   </si>
   <si>
@@ -1196,7 +1196,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1250,7 +1250,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -1345,7 +1345,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|4.0.1|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0-ballot-2|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1707,7 +1707,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-height-meas-method|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-height-meas-method|2.2.0</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2428,7 +2428,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="238.12109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="218.48046875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2443,7 +2443,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.9453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
